--- a/data/day1/real_buyers_ratios.xlsx
+++ b/data/day1/real_buyers_ratios.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>발췌 일치(정답 기준)</t>
+          <t>발췌 일치(기준 값)</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>실습 가이드 §1.10 정답(연간). 파산 신청 뒤 결산</t>
+          <t>연간 값(10-K). 파산 신청 뒤 결산</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>발췌 PART B(정답 기준)</t>
+          <t>발췌 PART B(기준 값)</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
